--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -47752,6 +47752,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2061">
+      <c r="A2061" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2061" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2061" t="n">
+        <v>0.272000014781952</v>
+      </c>
+      <c r="D2061" t="n">
+        <v>0.272000014781952</v>
+      </c>
+      <c r="E2061" t="n">
+        <v>0.272000014781952</v>
+      </c>
+      <c r="F2061" t="n">
+        <v>0.272000014781952</v>
+      </c>
+      <c r="G2061" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2062" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C2062" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="D2062" t="n">
+        <v>0.245000004768372</v>
+      </c>
+      <c r="E2062" t="n">
+        <v>0.245000004768372</v>
+      </c>
+      <c r="F2062" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="G2062" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -47798,6 +47798,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2063">
+      <c r="A2063" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2063" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2063" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="D2063" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="E2063" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="F2063" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="G2063" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -47662,22 +47662,22 @@
     </row>
     <row r="2057">
       <c r="A2057" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2057" t="n">
-        <v>19000</v>
+        <v>0</v>
       </c>
       <c r="C2057" t="n">
-        <v>0.280000001192093</v>
+        <v>0.272000014781952</v>
       </c>
       <c r="D2057" t="n">
-        <v>0.270000010728836</v>
+        <v>0.272000014781952</v>
       </c>
       <c r="E2057" t="n">
-        <v>0.270000010728836</v>
+        <v>0.272000014781952</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.280000001192093</v>
+        <v>0.272000014781952</v>
       </c>
       <c r="G2057" t="s">
         <v>7</v>
@@ -47685,16 +47685,16 @@
     </row>
     <row r="2058">
       <c r="A2058" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2058" t="n">
-        <v>49250</v>
+        <v>19000</v>
       </c>
       <c r="C2058" t="n">
         <v>0.280000001192093</v>
       </c>
       <c r="D2058" t="n">
-        <v>0.26800000667572</v>
+        <v>0.270000010728836</v>
       </c>
       <c r="E2058" t="n">
         <v>0.270000010728836</v>
@@ -47708,22 +47708,22 @@
     </row>
     <row r="2059">
       <c r="A2059" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2059" t="n">
-        <v>11250</v>
+        <v>49250</v>
       </c>
       <c r="C2059" t="n">
         <v>0.280000001192093</v>
       </c>
       <c r="D2059" t="n">
+        <v>0.26800000667572</v>
+      </c>
+      <c r="E2059" t="n">
         <v>0.270000010728836</v>
       </c>
-      <c r="E2059" t="n">
+      <c r="F2059" t="n">
         <v>0.280000001192093</v>
-      </c>
-      <c r="F2059" t="n">
-        <v>0.27700001001358</v>
       </c>
       <c r="G2059" t="s">
         <v>7</v>
@@ -47731,22 +47731,22 @@
     </row>
     <row r="2060">
       <c r="A2060" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2060" t="n">
-        <v>5250</v>
+        <v>11250</v>
       </c>
       <c r="C2060" t="n">
-        <v>0.272000014781952</v>
+        <v>0.280000001192093</v>
       </c>
       <c r="D2060" t="n">
-        <v>0.266000002622604</v>
+        <v>0.270000010728836</v>
       </c>
       <c r="E2060" t="n">
-        <v>0.266000002622604</v>
+        <v>0.280000001192093</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.272000014781952</v>
+        <v>0.27700001001358</v>
       </c>
       <c r="G2060" t="s">
         <v>7</v>
@@ -47754,19 +47754,19 @@
     </row>
     <row r="2061">
       <c r="A2061" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2061" t="n">
-        <v>0</v>
+        <v>5250</v>
       </c>
       <c r="C2061" t="n">
         <v>0.272000014781952</v>
       </c>
       <c r="D2061" t="n">
-        <v>0.272000014781952</v>
+        <v>0.266000002622604</v>
       </c>
       <c r="E2061" t="n">
-        <v>0.272000014781952</v>
+        <v>0.266000002622604</v>
       </c>
       <c r="F2061" t="n">
         <v>0.272000014781952</v>
@@ -47777,22 +47777,22 @@
     </row>
     <row r="2062">
       <c r="A2062" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2062" t="n">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="C2062" t="n">
-        <v>0.270000010728836</v>
+        <v>0.272000014781952</v>
       </c>
       <c r="D2062" t="n">
-        <v>0.245000004768372</v>
+        <v>0.272000014781952</v>
       </c>
       <c r="E2062" t="n">
-        <v>0.245000004768372</v>
+        <v>0.272000014781952</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.270000010728836</v>
+        <v>0.272000014781952</v>
       </c>
       <c r="G2062" t="s">
         <v>7</v>
@@ -47800,24 +47800,47 @@
     </row>
     <row r="2063">
       <c r="A2063" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2063" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="C2063" t="n">
         <v>0.270000010728836</v>
       </c>
       <c r="D2063" t="n">
-        <v>0.270000010728836</v>
+        <v>0.245000004768372</v>
       </c>
       <c r="E2063" t="n">
-        <v>0.270000010728836</v>
+        <v>0.245000004768372</v>
       </c>
       <c r="F2063" t="n">
         <v>0.270000010728836</v>
       </c>
       <c r="G2063" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2064" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2064" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="D2064" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="E2064" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="F2064" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="G2064" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -54117,6 +54117,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2068">
+      <c r="A2068" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2068" t="n">
+        <v>20500</v>
+      </c>
+      <c r="C2068" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="D2068" t="n">
+        <v>0.261999994516373</v>
+      </c>
+      <c r="E2068" t="n">
+        <v>0.261999994516373</v>
+      </c>
+      <c r="F2068" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="G2068" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="H2068" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -47936,6 +47936,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2069">
+      <c r="A2069" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2069" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2069" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="D2069" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="E2069" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="F2069" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="G2069" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -47959,6 +47959,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2070">
+      <c r="A2070" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2070" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2070" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="D2070" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="E2070" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="F2070" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="G2070" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -47982,6 +47982,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2071">
+      <c r="A2071" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2071" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2071" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="D2071" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="E2071" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="F2071" t="n">
+        <v>0.270000010728836</v>
+      </c>
+      <c r="G2071" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B2072" t="n">
+        <v>11250</v>
+      </c>
+      <c r="C2072" t="n">
+        <v>0.266999989748001</v>
+      </c>
+      <c r="D2072" t="n">
+        <v>0.256999999284744</v>
+      </c>
+      <c r="E2072" t="n">
+        <v>0.256999999284744</v>
+      </c>
+      <c r="F2072"/>
+      <c r="G2072" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -48021,7 +48021,9 @@
       <c r="E2072" t="n">
         <v>0.256999999284744</v>
       </c>
-      <c r="F2072"/>
+      <c r="F2072" t="n">
+        <v>0.266999989748001</v>
+      </c>
       <c r="G2072" t="s">
         <v>7</v>
       </c>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -48136,8 +48136,31 @@
       <c r="E2077" t="n">
         <v>0.228000000119209</v>
       </c>
-      <c r="F2077"/>
+      <c r="F2077" t="n">
+        <v>0.223000004887581</v>
+      </c>
       <c r="G2077" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2078" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C2078" t="n">
+        <v>0.226999998092651</v>
+      </c>
+      <c r="D2078" t="n">
+        <v>0.223000004887581</v>
+      </c>
+      <c r="E2078" t="n">
+        <v>0.223000004887581</v>
+      </c>
+      <c r="F2078"/>
+      <c r="G2078" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -48159,8 +48159,31 @@
       <c r="E2078" t="n">
         <v>0.223000004887581</v>
       </c>
-      <c r="F2078"/>
+      <c r="F2078" t="n">
+        <v>0.226999998092651</v>
+      </c>
       <c r="G2078" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2079" t="n">
+        <v>16250</v>
+      </c>
+      <c r="C2079" t="n">
+        <v>0.226999998092651</v>
+      </c>
+      <c r="D2079" t="n">
+        <v>0.216999992728233</v>
+      </c>
+      <c r="E2079" t="n">
+        <v>0.226999998092651</v>
+      </c>
+      <c r="F2079"/>
+      <c r="G2079" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -48182,8 +48182,31 @@
       <c r="E2079" t="n">
         <v>0.226999998092651</v>
       </c>
-      <c r="F2079"/>
+      <c r="F2079" t="n">
+        <v>0.223000004887581</v>
+      </c>
       <c r="G2079" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2080" t="n">
+        <v>11500</v>
+      </c>
+      <c r="C2080" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="D2080" t="n">
+        <v>0.216000005602837</v>
+      </c>
+      <c r="E2080" t="n">
+        <v>0.217999994754791</v>
+      </c>
+      <c r="F2080"/>
+      <c r="G2080" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -48205,8 +48205,31 @@
       <c r="E2080" t="n">
         <v>0.217999994754791</v>
       </c>
-      <c r="F2080"/>
+      <c r="F2080" t="n">
+        <v>0.218999996781349</v>
+      </c>
       <c r="G2080" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2081" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C2081" t="n">
+        <v>0.219999998807907</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>0.211999997496605</v>
+      </c>
+      <c r="E2081" t="n">
+        <v>0.216999992728233</v>
+      </c>
+      <c r="F2081"/>
+      <c r="G2081" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -48235,6 +48235,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2082">
+      <c r="A2082" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2082" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2082" t="n">
+        <v>0.215000003576279</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>0.215000003576279</v>
+      </c>
+      <c r="E2082" t="n">
+        <v>0.215000003576279</v>
+      </c>
+      <c r="F2082" t="n">
+        <v>0.215000003576279</v>
+      </c>
+      <c r="G2082" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -54559,6 +54559,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2085">
+      <c r="A2085" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2085" t="n">
+        <v>750</v>
+      </c>
+      <c r="C2085" t="n">
+        <v>0.211999997496605</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>0.204999998211861</v>
+      </c>
+      <c r="E2085" t="n">
+        <v>0.204999998211861</v>
+      </c>
+      <c r="F2085" t="n">
+        <v>0.211999997496605</v>
+      </c>
+      <c r="G2085" t="n">
+        <v>0.211999997496605</v>
+      </c>
+      <c r="H2085" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -54585,6 +54585,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2086">
+      <c r="A2086" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2086" t="n">
+        <v>114000</v>
+      </c>
+      <c r="C2086" t="n">
+        <v>0.209999993443489</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>0.199499994516373</v>
+      </c>
+      <c r="E2086" t="n">
+        <v>0.204999998211861</v>
+      </c>
+      <c r="F2086" t="n">
+        <v>0.208000004291534</v>
+      </c>
+      <c r="G2086" t="n">
+        <v>0.208000004291534</v>
+      </c>
+      <c r="H2086" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -60872,6 +60872,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2087">
+      <c r="A2087" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2087" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2087" t="n">
+        <v>0.199499994516373</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>0.199499994516373</v>
+      </c>
+      <c r="E2087" t="n">
+        <v>0.170000001788139</v>
+      </c>
+      <c r="F2087" t="n">
+        <v>0.170000001788139</v>
+      </c>
+      <c r="G2087" t="n">
+        <v>0.170000001788139</v>
+      </c>
+      <c r="H2087" t="n">
+        <v>76250</v>
+      </c>
+      <c r="I2087" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2088" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2088" t="n">
+        <v>0.160999998450279</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>0.180000007152557</v>
+      </c>
+      <c r="E2088" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="F2088" t="n">
+        <v>0.180000007152557</v>
+      </c>
+      <c r="G2088" t="n">
+        <v>0.180000007152557</v>
+      </c>
+      <c r="H2088" t="n">
+        <v>107500</v>
+      </c>
+      <c r="I2088" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -60930,6 +60930,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2089">
+      <c r="A2089" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2089" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2089" t="n">
+        <v>0.195500001311302</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>0.195500001311302</v>
+      </c>
+      <c r="E2089" t="n">
+        <v>0.185000002384186</v>
+      </c>
+      <c r="F2089" t="n">
+        <v>0.190999999642372</v>
+      </c>
+      <c r="G2089" t="n">
+        <v>0.190999999642372</v>
+      </c>
+      <c r="H2089" t="n">
+        <v>74500</v>
+      </c>
+      <c r="I2089" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -60953,9 +60953,38 @@
         <v>0.190999999642372</v>
       </c>
       <c r="H2089" t="n">
-        <v>74500</v>
+        <v>76000</v>
       </c>
       <c r="I2089" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2090" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2090" t="n">
+        <v>0.19200000166893</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>0.193000003695488</v>
+      </c>
+      <c r="E2090" t="n">
+        <v>0.19200000166893</v>
+      </c>
+      <c r="F2090" t="n">
+        <v>0.193000003695488</v>
+      </c>
+      <c r="G2090" t="n">
+        <v>0.193000003695488</v>
+      </c>
+      <c r="H2090" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I2090" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -60988,6 +60988,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2091">
+      <c r="A2091" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2091" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2091" t="n">
+        <v>0.195500001311302</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="E2091" t="n">
+        <v>0.195500001311302</v>
+      </c>
+      <c r="F2091" t="n">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="G2091" t="n">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="H2091" t="n">
+        <v>5250</v>
+      </c>
+      <c r="I2091" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -61017,6 +61017,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2092">
+      <c r="A2092" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2092" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2092" t="n">
+        <v>0.209999993443489</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>0.209999993443489</v>
+      </c>
+      <c r="E2092" t="n">
+        <v>0.209000006318092</v>
+      </c>
+      <c r="F2092" t="n">
+        <v>0.209999993443489</v>
+      </c>
+      <c r="G2092" t="n">
+        <v>0.209999993443489</v>
+      </c>
+      <c r="H2092" t="n">
+        <v>40500</v>
+      </c>
+      <c r="I2092" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -61046,6 +61046,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2093">
+      <c r="A2093" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2093" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2093" t="n">
+        <v>0.218999996781349</v>
+      </c>
+      <c r="D2093" t="n">
+        <v>0.223000004887581</v>
+      </c>
+      <c r="E2093" t="n">
+        <v>0.215000003576279</v>
+      </c>
+      <c r="F2093" t="n">
+        <v>0.223000004887581</v>
+      </c>
+      <c r="G2093" t="n">
+        <v>0.223000004887581</v>
+      </c>
+      <c r="H2093" t="n">
+        <v>15750</v>
+      </c>
+      <c r="I2093" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -61075,6 +61075,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2094">
+      <c r="A2094" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2094" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2094" t="n">
+        <v>0.223000004887581</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>0.223000004887581</v>
+      </c>
+      <c r="E2094" t="n">
+        <v>0.215000003576279</v>
+      </c>
+      <c r="F2094" t="n">
+        <v>0.215000003576279</v>
+      </c>
+      <c r="G2094" t="n">
+        <v>0.215000003576279</v>
+      </c>
+      <c r="H2094" t="n">
+        <v>15750</v>
+      </c>
+      <c r="I2094" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -61104,6 +61104,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2095">
+      <c r="A2095" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2095" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2095" t="n">
+        <v>0.215000003576279</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>0.215000003576279</v>
+      </c>
+      <c r="E2095" t="n">
+        <v>0.215000003576279</v>
+      </c>
+      <c r="F2095" t="n">
+        <v>0.215000003576279</v>
+      </c>
+      <c r="G2095" t="n">
+        <v>0.215000003576279</v>
+      </c>
+      <c r="H2095" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I2095" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOS.MI.xlsx
+++ b/data/SOS.MI.xlsx
@@ -61133,6 +61133,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2096">
+      <c r="A2096" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2096" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2096" t="n">
+        <v>0.195999994874001</v>
+      </c>
+      <c r="D2096" t="n">
+        <v>0.216000005602837</v>
+      </c>
+      <c r="E2096" t="n">
+        <v>0.195999994874001</v>
+      </c>
+      <c r="F2096" t="n">
+        <v>0.216000005602837</v>
+      </c>
+      <c r="G2096" t="n">
+        <v>0.216000005602837</v>
+      </c>
+      <c r="H2096" t="n">
+        <v>8250</v>
+      </c>
+      <c r="I2096" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
